--- a/docs/phase5/output/P5_DB시험_목록.xlsx
+++ b/docs/phase5/output/P5_DB시험_목록.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1879" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="784">
   <si>
     <t>DB 계약시험 목록</t>
   </si>
@@ -20,7 +20,7 @@
     <t>실행</t>
   </si>
   <si>
-    <t>2026-09-15 11:21  ·  full_test_run_20260915b.log</t>
+    <t>2026-09-15 11:50  ·  full_test_run_20260915c.log</t>
   </si>
   <si>
     <t>구획</t>
@@ -1364,6 +1364,12 @@
     <t>업무실패 6건 이후 @@TRANCOUNT = 0</t>
   </si>
   <si>
+    <t>RBK-008</t>
+  </si>
+  <si>
+    <t>실패 응답 RS 개수 - T-SQL 로 셀 수 없다. verify-docs V18 이 판정한다</t>
+  </si>
+  <si>
     <t>HLD-000</t>
   </si>
   <si>
@@ -2118,6 +2124,246 @@
   </si>
   <si>
     <t>재배포가 IDENTITY 시드를 감사기록 뒤로 이어받았다 (탐침 대상키 1000 → 시드 1000 · 탐침 정리 0건)</t>
+  </si>
+  <si>
+    <t>SEC-010</t>
+  </si>
+  <si>
+    <t>배포 원본·로그·보고서에 secret 0건</t>
+  </si>
+  <si>
+    <t>G13-c</t>
+  </si>
+  <si>
+    <t>§9.2 허용목록 검토 재생성 · 목록 밖 0건 (artifacts/reports/allowlist-review.md)</t>
+  </si>
+  <si>
+    <t>G00</t>
+  </si>
+  <si>
+    <t>기준선 7/7 · G01 WinForms 변경 0건(+변조 감지 자체시험) · G05 스키마↔04 양방향 대조</t>
+  </si>
+  <si>
+    <t>V01</t>
+  </si>
+  <si>
+    <t>코드펜스 짝 전부 일치</t>
+  </si>
+  <si>
+    <t>V02</t>
+  </si>
+  <si>
+    <t>placeholder 0건</t>
+  </si>
+  <si>
+    <t>V03c</t>
+  </si>
+  <si>
+    <t>카탈로그 범위 전개 247건 = 선언 합계</t>
+  </si>
+  <si>
+    <t>V03a</t>
+  </si>
+  <si>
+    <t>카탈로그 247건 전부 계획에 배치됨</t>
+  </si>
+  <si>
+    <t>V03b</t>
+  </si>
+  <si>
+    <t>계획 Test ID 전부 스펙에 근거 있음</t>
+  </si>
+  <si>
+    <t>V04</t>
+  </si>
+  <si>
+    <t>Fixture 23종 전부 생성 코드 있음</t>
+  </si>
+  <si>
+    <t>V05</t>
+  </si>
+  <si>
+    <t>금지 패턴 0건</t>
+  </si>
+  <si>
+    <t>V06</t>
+  </si>
+  <si>
+    <t>계획의 스펙 참조가 전부 v1.20</t>
+  </si>
+  <si>
+    <t>V07</t>
+  </si>
+  <si>
+    <t>오류번호 17종 전부 §20 에 등록됨</t>
+  </si>
+  <si>
+    <t>V08</t>
+  </si>
+  <si>
+    <t>제약 수치 일치 (CK=28 DF=10)</t>
+  </si>
+  <si>
+    <t>V09</t>
+  </si>
+  <si>
+    <t>산출물 28종 전부 §7 트리에 등재</t>
+  </si>
+  <si>
+    <t>V10</t>
+  </si>
+  <si>
+    <t>로그에 개인정보 자원명 출력 0건</t>
+  </si>
+  <si>
+    <t>V11</t>
+  </si>
+  <si>
+    <t>계획의 SP/TVF/Sequence/Table 참조 43종 전부 스펙·기준선에 정의됨</t>
+  </si>
+  <si>
+    <t>V12</t>
+  </si>
+  <si>
+    <t>완료조건이 건수를 재기술하지 않음 (§45.2 단일 출처)</t>
+  </si>
+  <si>
+    <t>V13</t>
+  </si>
+  <si>
+    <t>412 기대 테스트가 전부 EX012 보유 프로필을 쓴다 (§17.2a)</t>
+  </si>
+  <si>
+    <t>V14</t>
+  </si>
+  <si>
+    <t>계획 SQL 의 대괄호 식별자 전부 기준선에 실재</t>
+  </si>
+  <si>
+    <t>V15</t>
+  </si>
+  <si>
+    <t>R2 수치·식별자 사본 0건 (46개 파일)</t>
+  </si>
+  <si>
+    <t>V16</t>
+  </si>
+  <si>
+    <t>N 없는 리터럴에 CP949 밖 문자 0건 (292종 검사)</t>
+  </si>
+  <si>
+    <t>V17</t>
+  </si>
+  <si>
+    <t>RS0 블록 34개 전부 5컬럼 명시 CAST (4개 배포 파일)</t>
+  </si>
+  <si>
+    <t>V19</t>
+  </si>
+  <si>
+    <t>감사 INSERT 가 RS1 보다 앞 (Write SP 7개)</t>
+  </si>
+  <si>
+    <t>V18</t>
+  </si>
+  <si>
+    <t>RBK-008 실패 시나리오 69건 전부 RS0 1개만 (202·203 은 RS1 동반)</t>
+  </si>
+  <si>
+    <t>V20</t>
+  </si>
+  <si>
+    <t>화면·C# ↔ DB 이름 대응 30종 양방향 실재 (05 §16.5)</t>
+  </si>
+  <si>
+    <t>V21</t>
+  </si>
+  <si>
+    <t>지침 §참조 269건 전부 실재하는 절 (ROOT 10절 · database 11절)</t>
+  </si>
+  <si>
+    <t>V22</t>
+  </si>
+  <si>
+    <t>.sql 31개 전부 UTF-8 BOM (§5)</t>
+  </si>
+  <si>
+    <t>V23</t>
+  </si>
+  <si>
+    <t>살아 있는 문서 36개의 경로 참조 714건 전부 실재</t>
+  </si>
+  <si>
+    <t>V24</t>
+  </si>
+  <si>
+    <t>하드코딩 생성기 3개가 기준선보다 뒤처지지 않았다 (파싱형은 다시 돌리면 따라오므로 대상 아님)</t>
+  </si>
+  <si>
+    <t>V25</t>
+  </si>
+  <si>
+    <t>봉인 문서의 개수 주장 4건이 04 §7(테이블 7)·05 §1.3(SP 16)과 일치</t>
+  </si>
+  <si>
+    <t>V26</t>
+  </si>
+  <si>
+    <t>정책 시각값 주장 29건이 00 CP-04(09:00~18:00)·§3 마감(10:00/15:00 · 11:00/16:00)과 일치</t>
+  </si>
+  <si>
+    <t>V27</t>
+  </si>
+  <si>
+    <t>06 §18 SP Matrix 16행의 Param ↔ 01_Schema_Tests @ExpP · Result Set ↔ 05 선언 전건 일치</t>
+  </si>
+  <si>
+    <t>V28</t>
+  </si>
+  <si>
+    <t>06 문서 버전 v1.20 이 §1 과 §4.1 에서 일치</t>
+  </si>
+  <si>
+    <t>HOL-G1</t>
+  </si>
+  <si>
+    <t>00 §7.4 단일 출처: 등재 범위 2026-01-01 ~ 2027-12-31 · 경고 임계 잔여 180일</t>
+  </si>
+  <si>
+    <t>HOL-G2</t>
+  </si>
+  <si>
+    <t>Seed 41행 - 날짜 중복 0 · 구분 도메인 일치 · 범위 안 · 일요일 0 · 전부 활성</t>
+  </si>
+  <si>
+    <t>HOL-G3</t>
+  </si>
+  <si>
+    <t>06 §14 표 41행 = Seed 41행 (날짜·이름·구분 전건)</t>
+  </si>
+  <si>
+    <t>HOL-G4</t>
+  </si>
+  <si>
+    <t>SP 의 @경고임계일수 사본 = 00 §7.4 (180일)</t>
+  </si>
+  <si>
+    <t>HOL-G5</t>
+  </si>
+  <si>
+    <t>공휴일 등재 잔여 468일 &gt;= 임계 180일 (오늘 2026-09-15 · Seed 최종일 2027-12-27)</t>
+  </si>
+  <si>
+    <t>HOL-G6</t>
+  </si>
+  <si>
+    <t>00 §7.4 선언 끝 2027-12-31 과 Seed 최종일 2027-12-27 의 간격 4일 &lt;= 60일</t>
+  </si>
+  <si>
+    <t>RS-CONTRACT</t>
+  </si>
+  <si>
+    <t>기대값 Result Set 176개를 기준선 05 표와 대조 — 불일치 0건</t>
   </si>
 </sst>
 </file>
@@ -2745,13 +2991,13 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15">
         <v>8</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2813,10 +3059,10 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="C19">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -2830,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="B20" s="4">
-        <v>370</v>
+        <v>411</v>
       </c>
       <c r="C20" s="4">
-        <v>369</v>
+        <v>409</v>
       </c>
       <c r="D20" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="4">
         <v>0</v>
@@ -2850,7 +3096,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E371"/>
+  <dimension ref="A1:E412"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -6381,7 +6627,7 @@
     </row>
     <row r="208" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B208" s="5" t="s">
         <v>450</v>
@@ -6392,8 +6638,8 @@
       <c r="D208" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E208" s="6" t="s">
-        <v>5</v>
+      <c r="E208" s="7" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="209" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6424,7 +6670,7 @@
         <v>455</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>456</v>
+        <v>30</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>5</v>
@@ -6435,13 +6681,13 @@
         <v>19</v>
       </c>
       <c r="B211" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="C211" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="C211" s="5" t="s">
+      <c r="D211" s="5" t="s">
         <v>458</v>
-      </c>
-      <c r="D211" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="E211" s="6" t="s">
         <v>5</v>
@@ -6560,7 +6806,7 @@
         <v>472</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>473</v>
+        <v>30</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>5</v>
@@ -6571,13 +6817,13 @@
         <v>19</v>
       </c>
       <c r="B219" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="C219" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="C219" s="5" t="s">
+      <c r="D219" s="5" t="s">
         <v>475</v>
-      </c>
-      <c r="D219" s="5" t="s">
-        <v>476</v>
       </c>
       <c r="E219" s="6" t="s">
         <v>5</v>
@@ -6588,13 +6834,13 @@
         <v>19</v>
       </c>
       <c r="B220" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="C220" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="C220" s="5" t="s">
+      <c r="D220" s="5" t="s">
         <v>478</v>
-      </c>
-      <c r="D220" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>5</v>
@@ -6662,7 +6908,7 @@
         <v>486</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>487</v>
+        <v>30</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>5</v>
@@ -6673,13 +6919,13 @@
         <v>19</v>
       </c>
       <c r="B225" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="C225" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="C225" s="5" t="s">
+      <c r="D225" s="5" t="s">
         <v>489</v>
-      </c>
-      <c r="D225" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="E225" s="6" t="s">
         <v>5</v>
@@ -6687,7 +6933,7 @@
     </row>
     <row r="226" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B226" s="5" t="s">
         <v>490</v>
@@ -6755,7 +7001,7 @@
     </row>
     <row r="230" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B230" s="5" t="s">
         <v>498</v>
@@ -6778,7 +7024,7 @@
         <v>500</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D231" s="5" t="s">
         <v>30</v>
@@ -6792,10 +7038,10 @@
         <v>21</v>
       </c>
       <c r="B232" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="C232" s="5" t="s">
         <v>501</v>
-      </c>
-      <c r="C232" s="5" t="s">
-        <v>499</v>
       </c>
       <c r="D232" s="5" t="s">
         <v>30</v>
@@ -6809,10 +7055,10 @@
         <v>21</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D233" s="5" t="s">
         <v>30</v>
@@ -6826,10 +7072,10 @@
         <v>21</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D234" s="5" t="s">
         <v>30</v>
@@ -6843,10 +7089,10 @@
         <v>21</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="D235" s="5" t="s">
         <v>30</v>
@@ -6897,7 +7143,7 @@
         <v>510</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="D238" s="5" t="s">
         <v>30</v>
@@ -6911,10 +7157,10 @@
         <v>21</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="D239" s="5" t="s">
         <v>30</v>
@@ -6999,7 +7245,7 @@
         <v>521</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="D244" s="5" t="s">
         <v>30</v>
@@ -7013,10 +7259,10 @@
         <v>21</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D245" s="5" t="s">
         <v>30</v>
@@ -7030,10 +7276,10 @@
         <v>21</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D246" s="5" t="s">
         <v>30</v>
@@ -7047,10 +7293,10 @@
         <v>21</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D247" s="5" t="s">
         <v>30</v>
@@ -7064,10 +7310,10 @@
         <v>21</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D248" s="5" t="s">
         <v>30</v>
@@ -7081,10 +7327,10 @@
         <v>21</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D249" s="5" t="s">
         <v>30</v>
@@ -7098,10 +7344,10 @@
         <v>21</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D250" s="5" t="s">
         <v>30</v>
@@ -7112,13 +7358,13 @@
     </row>
     <row r="251" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D251" s="5" t="s">
         <v>30</v>
@@ -7135,7 +7381,7 @@
         <v>530</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="D252" s="5" t="s">
         <v>30</v>
@@ -7149,10 +7395,10 @@
         <v>20</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>532</v>
+        <v>514</v>
       </c>
       <c r="D253" s="5" t="s">
         <v>30</v>
@@ -7203,7 +7449,7 @@
         <v>537</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>514</v>
+        <v>538</v>
       </c>
       <c r="D256" s="5" t="s">
         <v>30</v>
@@ -7217,10 +7463,10 @@
         <v>20</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="D257" s="5" t="s">
         <v>30</v>
@@ -7234,10 +7480,10 @@
         <v>20</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>536</v>
+        <v>501</v>
       </c>
       <c r="D258" s="5" t="s">
         <v>30</v>
@@ -7251,10 +7497,10 @@
         <v>20</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="D259" s="5" t="s">
         <v>30</v>
@@ -7268,10 +7514,10 @@
         <v>20</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="D260" s="5" t="s">
         <v>30</v>
@@ -7288,7 +7534,7 @@
         <v>543</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>514</v>
+        <v>544</v>
       </c>
       <c r="D261" s="5" t="s">
         <v>30</v>
@@ -7302,10 +7548,10 @@
         <v>20</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>545</v>
+        <v>516</v>
       </c>
       <c r="D262" s="5" t="s">
         <v>30</v>
@@ -7322,7 +7568,7 @@
         <v>546</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>499</v>
+        <v>547</v>
       </c>
       <c r="D263" s="5" t="s">
         <v>30</v>
@@ -7336,10 +7582,10 @@
         <v>20</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D264" s="5" t="s">
         <v>30</v>
@@ -7353,10 +7599,10 @@
         <v>20</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>549</v>
+        <v>501</v>
       </c>
       <c r="D265" s="5" t="s">
         <v>30</v>
@@ -7390,7 +7636,7 @@
         <v>552</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>536</v>
+        <v>553</v>
       </c>
       <c r="D267" s="5" t="s">
         <v>30</v>
@@ -7404,10 +7650,10 @@
         <v>20</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="D268" s="5" t="s">
         <v>30</v>
@@ -7421,7 +7667,7 @@
         <v>20</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C269" s="5" t="s">
         <v>536</v>
@@ -7438,10 +7684,10 @@
         <v>20</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="D270" s="5" t="s">
         <v>30</v>
@@ -7455,10 +7701,10 @@
         <v>20</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>499</v>
+        <v>536</v>
       </c>
       <c r="D271" s="5" t="s">
         <v>30</v>
@@ -7472,10 +7718,10 @@
         <v>20</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>536</v>
+        <v>501</v>
       </c>
       <c r="D272" s="5" t="s">
         <v>30</v>
@@ -7489,10 +7735,10 @@
         <v>20</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D273" s="5" t="s">
         <v>30</v>
@@ -7506,10 +7752,10 @@
         <v>20</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="D274" s="5" t="s">
         <v>30</v>
@@ -7523,10 +7769,10 @@
         <v>20</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>561</v>
+        <v>531</v>
       </c>
       <c r="D275" s="5" t="s">
         <v>30</v>
@@ -7543,7 +7789,7 @@
         <v>562</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>520</v>
+        <v>563</v>
       </c>
       <c r="D276" s="5" t="s">
         <v>30</v>
@@ -7557,10 +7803,10 @@
         <v>20</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
       <c r="D277" s="5" t="s">
         <v>30</v>
@@ -7574,10 +7820,10 @@
         <v>20</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D278" s="5" t="s">
         <v>30</v>
@@ -7591,10 +7837,10 @@
         <v>20</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>566</v>
+        <v>507</v>
       </c>
       <c r="D279" s="5" t="s">
         <v>30</v>
@@ -7645,7 +7891,7 @@
         <v>571</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>505</v>
+        <v>572</v>
       </c>
       <c r="D282" s="5" t="s">
         <v>30</v>
@@ -7659,10 +7905,10 @@
         <v>20</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>573</v>
+        <v>507</v>
       </c>
       <c r="D283" s="5" t="s">
         <v>30</v>
@@ -7696,7 +7942,7 @@
         <v>576</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>529</v>
+        <v>577</v>
       </c>
       <c r="D285" s="5" t="s">
         <v>30</v>
@@ -7710,10 +7956,10 @@
         <v>20</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>499</v>
+        <v>531</v>
       </c>
       <c r="D286" s="5" t="s">
         <v>30</v>
@@ -7727,10 +7973,10 @@
         <v>20</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D287" s="5" t="s">
         <v>30</v>
@@ -7764,7 +8010,7 @@
         <v>582</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>505</v>
+        <v>583</v>
       </c>
       <c r="D289" s="5" t="s">
         <v>30</v>
@@ -7778,10 +8024,10 @@
         <v>20</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D290" s="5" t="s">
         <v>30</v>
@@ -7795,10 +8041,10 @@
         <v>20</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="D291" s="5" t="s">
         <v>30</v>
@@ -7812,10 +8058,10 @@
         <v>20</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>586</v>
+        <v>520</v>
       </c>
       <c r="D292" s="5" t="s">
         <v>30</v>
@@ -7849,7 +8095,7 @@
         <v>589</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>499</v>
+        <v>590</v>
       </c>
       <c r="D294" s="5" t="s">
         <v>30</v>
@@ -7863,10 +8109,10 @@
         <v>20</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D295" s="5" t="s">
         <v>30</v>
@@ -7880,10 +8126,10 @@
         <v>20</v>
       </c>
       <c r="B296" s="5" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>505</v>
+        <v>581</v>
       </c>
       <c r="D296" s="5" t="s">
         <v>30</v>
@@ -7897,10 +8143,10 @@
         <v>20</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>545</v>
+        <v>507</v>
       </c>
       <c r="D297" s="5" t="s">
         <v>30</v>
@@ -7914,10 +8160,10 @@
         <v>20</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="D298" s="5" t="s">
         <v>30</v>
@@ -7931,10 +8177,10 @@
         <v>20</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>499</v>
+        <v>536</v>
       </c>
       <c r="D299" s="5" t="s">
         <v>30</v>
@@ -7948,10 +8194,10 @@
         <v>20</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>596</v>
+        <v>501</v>
       </c>
       <c r="D300" s="5" t="s">
         <v>30</v>
@@ -7968,7 +8214,7 @@
         <v>597</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>499</v>
+        <v>598</v>
       </c>
       <c r="D301" s="5" t="s">
         <v>30</v>
@@ -7982,10 +8228,10 @@
         <v>20</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>599</v>
+        <v>501</v>
       </c>
       <c r="D302" s="5" t="s">
         <v>30</v>
@@ -8019,7 +8265,7 @@
         <v>602</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="D304" s="5" t="s">
         <v>30</v>
@@ -8033,10 +8279,10 @@
         <v>20</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>499</v>
+        <v>598</v>
       </c>
       <c r="D305" s="5" t="s">
         <v>30</v>
@@ -8050,10 +8296,10 @@
         <v>20</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>529</v>
+        <v>501</v>
       </c>
       <c r="D306" s="5" t="s">
         <v>30</v>
@@ -8067,10 +8313,10 @@
         <v>20</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D307" s="5" t="s">
         <v>30</v>
@@ -8084,10 +8330,10 @@
         <v>20</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>607</v>
+        <v>531</v>
       </c>
       <c r="D308" s="5" t="s">
         <v>30</v>
@@ -8155,7 +8401,7 @@
         <v>614</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>518</v>
+        <v>615</v>
       </c>
       <c r="D312" s="5" t="s">
         <v>30</v>
@@ -8169,10 +8415,10 @@
         <v>20</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>616</v>
+        <v>520</v>
       </c>
       <c r="D313" s="5" t="s">
         <v>30</v>
@@ -8189,7 +8435,7 @@
         <v>617</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>549</v>
+        <v>618</v>
       </c>
       <c r="D314" s="5" t="s">
         <v>30</v>
@@ -8203,10 +8449,10 @@
         <v>20</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>499</v>
+        <v>551</v>
       </c>
       <c r="D315" s="5" t="s">
         <v>30</v>
@@ -8220,10 +8466,10 @@
         <v>20</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>620</v>
+        <v>501</v>
       </c>
       <c r="D316" s="5" t="s">
         <v>30</v>
@@ -8240,7 +8486,7 @@
         <v>621</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>514</v>
+        <v>622</v>
       </c>
       <c r="D317" s="5" t="s">
         <v>30</v>
@@ -8254,10 +8500,10 @@
         <v>20</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>623</v>
+        <v>516</v>
       </c>
       <c r="D318" s="5" t="s">
         <v>30</v>
@@ -8274,7 +8520,7 @@
         <v>624</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>545</v>
+        <v>625</v>
       </c>
       <c r="D319" s="5" t="s">
         <v>30</v>
@@ -8288,10 +8534,10 @@
         <v>20</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>499</v>
+        <v>547</v>
       </c>
       <c r="D320" s="5" t="s">
         <v>30</v>
@@ -8305,10 +8551,10 @@
         <v>20</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D321" s="5" t="s">
         <v>30</v>
@@ -8322,10 +8568,10 @@
         <v>20</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D322" s="5" t="s">
         <v>30</v>
@@ -8339,10 +8585,10 @@
         <v>20</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D323" s="5" t="s">
         <v>30</v>
@@ -8356,10 +8602,10 @@
         <v>20</v>
       </c>
       <c r="B324" s="5" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>534</v>
+        <v>501</v>
       </c>
       <c r="D324" s="5" t="s">
         <v>30</v>
@@ -8373,7 +8619,7 @@
         <v>20</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C325" s="5" t="s">
         <v>536</v>
@@ -8390,10 +8636,10 @@
         <v>20</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>512</v>
+        <v>538</v>
       </c>
       <c r="D326" s="5" t="s">
         <v>30</v>
@@ -8407,10 +8653,10 @@
         <v>20</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="D327" s="5" t="s">
         <v>30</v>
@@ -8424,10 +8670,10 @@
         <v>20</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>634</v>
+        <v>501</v>
       </c>
       <c r="D328" s="5" t="s">
         <v>30</v>
@@ -8444,7 +8690,7 @@
         <v>635</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>499</v>
+        <v>636</v>
       </c>
       <c r="D329" s="5" t="s">
         <v>30</v>
@@ -8458,10 +8704,10 @@
         <v>20</v>
       </c>
       <c r="B330" s="5" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>551</v>
+        <v>501</v>
       </c>
       <c r="D330" s="5" t="s">
         <v>30</v>
@@ -8475,10 +8721,10 @@
         <v>20</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>620</v>
+        <v>553</v>
       </c>
       <c r="D331" s="5" t="s">
         <v>30</v>
@@ -8492,10 +8738,10 @@
         <v>20</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>514</v>
+        <v>622</v>
       </c>
       <c r="D332" s="5" t="s">
         <v>30</v>
@@ -8509,10 +8755,10 @@
         <v>20</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D333" s="5" t="s">
         <v>30</v>
@@ -8526,10 +8772,10 @@
         <v>20</v>
       </c>
       <c r="B334" s="5" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="D334" s="5" t="s">
         <v>30</v>
@@ -8543,10 +8789,10 @@
         <v>20</v>
       </c>
       <c r="B335" s="5" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>534</v>
+        <v>514</v>
       </c>
       <c r="D335" s="5" t="s">
         <v>30</v>
@@ -8560,7 +8806,7 @@
         <v>20</v>
       </c>
       <c r="B336" s="5" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C336" s="5" t="s">
         <v>536</v>
@@ -8577,10 +8823,10 @@
         <v>20</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>499</v>
+        <v>538</v>
       </c>
       <c r="D337" s="5" t="s">
         <v>30</v>
@@ -8594,10 +8840,10 @@
         <v>20</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>529</v>
+        <v>501</v>
       </c>
       <c r="D338" s="5" t="s">
         <v>30</v>
@@ -8611,10 +8857,10 @@
         <v>20</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>499</v>
+        <v>531</v>
       </c>
       <c r="D339" s="5" t="s">
         <v>30</v>
@@ -8628,10 +8874,10 @@
         <v>20</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D340" s="5" t="s">
         <v>30</v>
@@ -8645,10 +8891,10 @@
         <v>20</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="D341" s="5" t="s">
         <v>30</v>
@@ -8662,10 +8908,10 @@
         <v>20</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="D342" s="5" t="s">
         <v>30</v>
@@ -8679,10 +8925,10 @@
         <v>20</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>650</v>
+        <v>522</v>
       </c>
       <c r="D343" s="5" t="s">
         <v>30</v>
@@ -8693,7 +8939,7 @@
     </row>
     <row r="344" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A344" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B344" s="5" t="s">
         <v>651</v>
@@ -8784,7 +9030,7 @@
         <v>661</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="D349" s="5" t="s">
         <v>30</v>
@@ -8798,10 +9044,10 @@
         <v>22</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="D350" s="5" t="s">
         <v>30</v>
@@ -8818,7 +9064,7 @@
         <v>664</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="D351" s="5" t="s">
         <v>30</v>
@@ -8832,10 +9078,10 @@
         <v>22</v>
       </c>
       <c r="B352" s="5" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D352" s="5" t="s">
         <v>30</v>
@@ -8852,7 +9098,7 @@
         <v>667</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>658</v>
+        <v>668</v>
       </c>
       <c r="D353" s="5" t="s">
         <v>30</v>
@@ -8866,10 +9112,10 @@
         <v>22</v>
       </c>
       <c r="B354" s="5" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="D354" s="5" t="s">
         <v>30</v>
@@ -8971,7 +9217,7 @@
         <v>680</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>658</v>
+        <v>681</v>
       </c>
       <c r="D360" s="5" t="s">
         <v>30</v>
@@ -8985,10 +9231,10 @@
         <v>22</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>682</v>
+        <v>660</v>
       </c>
       <c r="D361" s="5" t="s">
         <v>30</v>
@@ -9002,10 +9248,10 @@
         <v>22</v>
       </c>
       <c r="B362" s="5" t="s">
-        <v>651</v>
+        <v>683</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D362" s="5" t="s">
         <v>30</v>
@@ -9019,7 +9265,7 @@
         <v>22</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>684</v>
+        <v>653</v>
       </c>
       <c r="C363" s="5" t="s">
         <v>685</v>
@@ -9061,8 +9307,8 @@
       <c r="D365" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E365" s="7" t="s">
-        <v>6</v>
+      <c r="E365" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="366" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -9078,8 +9324,8 @@
       <c r="D366" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E366" s="6" t="s">
-        <v>5</v>
+      <c r="E366" s="7" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="367" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -9164,6 +9410,703 @@
         <v>30</v>
       </c>
       <c r="E371" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A372" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B372" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="C372" s="5" t="s">
+        <v>703</v>
+      </c>
+      <c r="D372" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E372" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A373" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B373" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="C373" s="5" t="s">
+        <v>705</v>
+      </c>
+      <c r="D373" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E373" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A374" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B374" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="C374" s="5" t="s">
+        <v>707</v>
+      </c>
+      <c r="D374" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E374" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A375" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B375" s="5" t="s">
+        <v>708</v>
+      </c>
+      <c r="C375" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="D375" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E375" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A376" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B376" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="C376" s="5" t="s">
+        <v>711</v>
+      </c>
+      <c r="D376" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E376" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A377" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B377" s="5" t="s">
+        <v>712</v>
+      </c>
+      <c r="C377" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D377" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E377" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A378" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B378" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="C378" s="5" t="s">
+        <v>715</v>
+      </c>
+      <c r="D378" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E378" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A379" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B379" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="C379" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="D379" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E379" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A380" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B380" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="C380" s="5" t="s">
+        <v>719</v>
+      </c>
+      <c r="D380" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E380" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A381" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B381" s="5" t="s">
+        <v>720</v>
+      </c>
+      <c r="C381" s="5" t="s">
+        <v>721</v>
+      </c>
+      <c r="D381" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E381" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A382" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B382" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="C382" s="5" t="s">
+        <v>723</v>
+      </c>
+      <c r="D382" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E382" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A383" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B383" s="5" t="s">
+        <v>724</v>
+      </c>
+      <c r="C383" s="5" t="s">
+        <v>725</v>
+      </c>
+      <c r="D383" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E383" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A384" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B384" s="5" t="s">
+        <v>726</v>
+      </c>
+      <c r="C384" s="5" t="s">
+        <v>727</v>
+      </c>
+      <c r="D384" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E384" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A385" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B385" s="5" t="s">
+        <v>728</v>
+      </c>
+      <c r="C385" s="5" t="s">
+        <v>729</v>
+      </c>
+      <c r="D385" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E385" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A386" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B386" s="5" t="s">
+        <v>730</v>
+      </c>
+      <c r="C386" s="5" t="s">
+        <v>731</v>
+      </c>
+      <c r="D386" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E386" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A387" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B387" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="C387" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="D387" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E387" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A388" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B388" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="C388" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="D388" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E388" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A389" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B389" s="5" t="s">
+        <v>736</v>
+      </c>
+      <c r="C389" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="D389" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E389" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A390" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B390" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="C390" s="5" t="s">
+        <v>739</v>
+      </c>
+      <c r="D390" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E390" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A391" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B391" s="5" t="s">
+        <v>740</v>
+      </c>
+      <c r="C391" s="5" t="s">
+        <v>741</v>
+      </c>
+      <c r="D391" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E391" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A392" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B392" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C392" s="5" t="s">
+        <v>743</v>
+      </c>
+      <c r="D392" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E392" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A393" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B393" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="C393" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="D393" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E393" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A394" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B394" s="5" t="s">
+        <v>746</v>
+      </c>
+      <c r="C394" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="D394" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E394" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A395" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B395" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="C395" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="D395" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E395" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A396" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B396" s="5" t="s">
+        <v>750</v>
+      </c>
+      <c r="C396" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="D396" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E396" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A397" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B397" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="C397" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="D397" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E397" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A398" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B398" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="C398" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="D398" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E398" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A399" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B399" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="C399" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="D399" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E399" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A400" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B400" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="C400" s="5" t="s">
+        <v>759</v>
+      </c>
+      <c r="D400" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E400" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A401" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B401" s="5" t="s">
+        <v>760</v>
+      </c>
+      <c r="C401" s="5" t="s">
+        <v>761</v>
+      </c>
+      <c r="D401" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E401" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A402" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B402" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="C402" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="D402" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E402" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A403" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B403" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="C403" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="D403" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E403" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A404" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B404" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="C404" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="D404" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E404" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A405" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B405" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="C405" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="D405" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E405" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A406" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B406" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="C406" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="D406" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E406" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A407" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B407" s="5" t="s">
+        <v>772</v>
+      </c>
+      <c r="C407" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="D407" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E407" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A408" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B408" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="C408" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="D408" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E408" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A409" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B409" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="C409" s="5" t="s">
+        <v>777</v>
+      </c>
+      <c r="D409" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E409" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A410" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B410" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="C410" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="D410" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E410" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A411" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B411" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="C411" s="5" t="s">
+        <v>781</v>
+      </c>
+      <c r="D411" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E411" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A412" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B412" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="C412" s="5" t="s">
+        <v>783</v>
+      </c>
+      <c r="D412" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E412" s="6" t="s">
         <v>5</v>
       </c>
     </row>
